--- a/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
+++ b/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
+++ b/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
+++ b/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
+++ b/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Le local s’inscrit dans un programme neuf à usage principal d’habitation, développant plusieurs niveaux et situé au sein d’un environnement urbain dynamique du Pré-Saint-Gervais. L’immeuble bénéficie d’une architecture contemporaine et d’une implantation dans un secteur résidentiel animé, à proximité immédiate des commerces et des transports. La livraison prévisionnelle est fixée au quatrième trimestre 2027, garantissant des prestations modernes et conformes aux dernières normes de construction.</t>
+          <t>Surface du lot : 148,03 m² + jardins Prix de vente : 472 704 € HT Frais d’agence: 5 % HT du prix de vente HT à la charge de l’acquéreur Surface du lot : 89,19 m² Prix de vente : 266 970 € HT Frais d’agence: 5 % HT du prix de vente HT à la charge de l’acquéreur Le local s’inscrit dans un programme neuf à usage principal d’habitation, développant plusieurs niveaux et situé au sein d’un environnement urbain dynamique du Pré-Saint-Gervais. L’immeuble bénéficie d’une architecture contemporaine et d’une implantation dans un secteur résidentiel animé, à proximité immédiate des commerces et des transports. La livraison prévisionnelle est fixée au quatrième trimestre 2027, garantissant des prestations modernes et conformes aux dernières normes de construction.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
+++ b/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
+++ b/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +195 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +176 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="30">

--- a/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
+++ b/docs/dossiers/dossier-le-pre-saint-gervais-5dad2e65.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
